--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M151"/>
+  <dimension ref="A1:M152"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6029,6 +6029,43 @@
         <v>195.49</v>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>1754.36</v>
+      </c>
+      <c r="D152" t="n">
+        <v>1574.27</v>
+      </c>
+      <c r="E152" t="n">
+        <v>324.55</v>
+      </c>
+      <c r="F152" t="n">
+        <v>196.09</v>
+      </c>
+      <c r="G152" t="n">
+        <v>294.29</v>
+      </c>
+      <c r="H152" t="n">
+        <v>1694.5</v>
+      </c>
+      <c r="J152" t="n">
+        <v>1621</v>
+      </c>
+      <c r="K152" t="n">
+        <v>145.93</v>
+      </c>
+      <c r="L152" t="n">
+        <v>154.99</v>
+      </c>
+      <c r="M152" t="n">
+        <v>195.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M152"/>
+  <dimension ref="A1:M153"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6066,6 +6066,43 @@
         <v>195.49</v>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>1754.36</v>
+      </c>
+      <c r="D153" t="n">
+        <v>1448230.25</v>
+      </c>
+      <c r="E153" t="n">
+        <v>312.3</v>
+      </c>
+      <c r="F153" t="n">
+        <v>168.59</v>
+      </c>
+      <c r="G153" t="n">
+        <v>294.29</v>
+      </c>
+      <c r="H153" t="n">
+        <v>1694.5</v>
+      </c>
+      <c r="J153" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K153" t="n">
+        <v>140.99</v>
+      </c>
+      <c r="L153" t="n">
+        <v>154.99</v>
+      </c>
+      <c r="M153" t="n">
+        <v>195.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M153"/>
+  <dimension ref="A1:M154"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6103,6 +6103,43 @@
         <v>195.49</v>
       </c>
     </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>1754.36</v>
+      </c>
+      <c r="D154" t="n">
+        <v>1479018.57</v>
+      </c>
+      <c r="E154" t="n">
+        <v>315.11</v>
+      </c>
+      <c r="F154" t="n">
+        <v>177.22</v>
+      </c>
+      <c r="G154" t="n">
+        <v>169.06</v>
+      </c>
+      <c r="H154" t="n">
+        <v>1694.5</v>
+      </c>
+      <c r="J154" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K154" t="n">
+        <v>145.93</v>
+      </c>
+      <c r="L154" t="n">
+        <v>157.81</v>
+      </c>
+      <c r="M154" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M154"/>
+  <dimension ref="A1:M155"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6140,6 +6140,43 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>1754.36</v>
+      </c>
+      <c r="D155" t="n">
+        <v>1479018.57</v>
+      </c>
+      <c r="E155" t="n">
+        <v>393.94</v>
+      </c>
+      <c r="F155" t="n">
+        <v>162.46</v>
+      </c>
+      <c r="G155" t="n">
+        <v>169.06</v>
+      </c>
+      <c r="H155" t="n">
+        <v>1694.5</v>
+      </c>
+      <c r="J155" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K155" t="n">
+        <v>135.97</v>
+      </c>
+      <c r="L155" t="n">
+        <v>145.26</v>
+      </c>
+      <c r="M155" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M155"/>
+  <dimension ref="A1:M156"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6177,6 +6177,43 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>1754.36</v>
+      </c>
+      <c r="D156" t="n">
+        <v>1479018.57</v>
+      </c>
+      <c r="E156" t="n">
+        <v>315.52</v>
+      </c>
+      <c r="F156" t="n">
+        <v>139.88</v>
+      </c>
+      <c r="G156" t="n">
+        <v>169.06</v>
+      </c>
+      <c r="H156" t="n">
+        <v>1694.5</v>
+      </c>
+      <c r="J156" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K156" t="n">
+        <v>130.94</v>
+      </c>
+      <c r="L156" t="n">
+        <v>143.99</v>
+      </c>
+      <c r="M156" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M156"/>
+  <dimension ref="A1:M157"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6214,6 +6214,43 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>1755.9</v>
+      </c>
+      <c r="D157" t="n">
+        <v>1479016.83</v>
+      </c>
+      <c r="E157" t="n">
+        <v>315.52</v>
+      </c>
+      <c r="F157" t="n">
+        <v>145.54</v>
+      </c>
+      <c r="G157" t="n">
+        <v>169.32</v>
+      </c>
+      <c r="H157" t="n">
+        <v>1690</v>
+      </c>
+      <c r="J157" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K157" t="n">
+        <v>130.94</v>
+      </c>
+      <c r="L157" t="n">
+        <v>149.27</v>
+      </c>
+      <c r="M157" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M157"/>
+  <dimension ref="A1:M158"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6251,6 +6251,43 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>1755.9</v>
+      </c>
+      <c r="D158" t="n">
+        <v>1479016.83</v>
+      </c>
+      <c r="E158" t="n">
+        <v>315.52</v>
+      </c>
+      <c r="F158" t="n">
+        <v>146.38</v>
+      </c>
+      <c r="G158" t="n">
+        <v>169.32</v>
+      </c>
+      <c r="H158" t="n">
+        <v>1690</v>
+      </c>
+      <c r="J158" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K158" t="n">
+        <v>130.94</v>
+      </c>
+      <c r="L158" t="n">
+        <v>149.27</v>
+      </c>
+      <c r="M158" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M158"/>
+  <dimension ref="A1:M159"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6288,6 +6288,43 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>1755.9</v>
+      </c>
+      <c r="D159" t="n">
+        <v>1479016.83</v>
+      </c>
+      <c r="E159" t="n">
+        <v>315.52</v>
+      </c>
+      <c r="F159" t="n">
+        <v>180.22</v>
+      </c>
+      <c r="G159" t="n">
+        <v>169.32</v>
+      </c>
+      <c r="H159" t="n">
+        <v>1690</v>
+      </c>
+      <c r="J159" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K159" t="n">
+        <v>130.94</v>
+      </c>
+      <c r="L159" t="n">
+        <v>157.81</v>
+      </c>
+      <c r="M159" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M159"/>
+  <dimension ref="A1:M160"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6325,6 +6325,43 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>1755.9</v>
+      </c>
+      <c r="D160" t="n">
+        <v>1479016.83</v>
+      </c>
+      <c r="E160" t="n">
+        <v>315.52</v>
+      </c>
+      <c r="F160" t="n">
+        <v>144.19</v>
+      </c>
+      <c r="G160" t="n">
+        <v>169.06</v>
+      </c>
+      <c r="H160" t="n">
+        <v>1690</v>
+      </c>
+      <c r="J160" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K160" t="n">
+        <v>130.94</v>
+      </c>
+      <c r="L160" t="n">
+        <v>143.95</v>
+      </c>
+      <c r="M160" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M160"/>
+  <dimension ref="A1:M161"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6362,6 +6362,43 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>1734.19</v>
+      </c>
+      <c r="D161" t="n">
+        <v>1479016.83</v>
+      </c>
+      <c r="E161" t="n">
+        <v>315.52</v>
+      </c>
+      <c r="F161" t="n">
+        <v>143.12</v>
+      </c>
+      <c r="G161" t="n">
+        <v>169.06</v>
+      </c>
+      <c r="H161" t="n">
+        <v>1599</v>
+      </c>
+      <c r="J161" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K161" t="n">
+        <v>130.94</v>
+      </c>
+      <c r="L161" t="n">
+        <v>143.95</v>
+      </c>
+      <c r="M161" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M161"/>
+  <dimension ref="A1:M162"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6399,6 +6399,43 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>1749.47</v>
+      </c>
+      <c r="D162" t="n">
+        <v>1479016.83</v>
+      </c>
+      <c r="E162" t="n">
+        <v>306.41</v>
+      </c>
+      <c r="F162" t="n">
+        <v>147.89</v>
+      </c>
+      <c r="G162" t="n">
+        <v>269.29</v>
+      </c>
+      <c r="H162" t="n">
+        <v>1694.5</v>
+      </c>
+      <c r="J162" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K162" t="n">
+        <v>130.61</v>
+      </c>
+      <c r="L162" t="n">
+        <v>154.11</v>
+      </c>
+      <c r="M162" t="n">
+        <v>195.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M162"/>
+  <dimension ref="A1:M163"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6436,6 +6436,43 @@
         <v>195.49</v>
       </c>
     </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>1736.84</v>
+      </c>
+      <c r="D163" t="n">
+        <v>1479016.83</v>
+      </c>
+      <c r="E163" t="n">
+        <v>276.12</v>
+      </c>
+      <c r="F163" t="n">
+        <v>149.31</v>
+      </c>
+      <c r="G163" t="n">
+        <v>269.29</v>
+      </c>
+      <c r="H163" t="n">
+        <v>1690</v>
+      </c>
+      <c r="J163" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K163" t="n">
+        <v>130.3</v>
+      </c>
+      <c r="L163" t="n">
+        <v>152.23</v>
+      </c>
+      <c r="M163" t="n">
+        <v>195.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M163"/>
+  <dimension ref="A1:M164"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6473,6 +6473,43 @@
         <v>195.49</v>
       </c>
     </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>1749.47</v>
+      </c>
+      <c r="D164" t="n">
+        <v>1479016.83</v>
+      </c>
+      <c r="E164" t="n">
+        <v>267.35</v>
+      </c>
+      <c r="F164" t="n">
+        <v>149.6</v>
+      </c>
+      <c r="G164" t="n">
+        <v>269.29</v>
+      </c>
+      <c r="H164" t="n">
+        <v>1694.5</v>
+      </c>
+      <c r="J164" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K164" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="L164" t="n">
+        <v>156.99</v>
+      </c>
+      <c r="M164" t="n">
+        <v>195.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M164"/>
+  <dimension ref="A1:M165"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6510,6 +6510,43 @@
         <v>195.49</v>
       </c>
     </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>1736.84</v>
+      </c>
+      <c r="D165" t="n">
+        <v>1479016.83</v>
+      </c>
+      <c r="E165" t="n">
+        <v>263.24</v>
+      </c>
+      <c r="F165" t="n">
+        <v>141.87</v>
+      </c>
+      <c r="G165" t="n">
+        <v>269.29</v>
+      </c>
+      <c r="H165" t="n">
+        <v>1690</v>
+      </c>
+      <c r="J165" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K165" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="L165" t="n">
+        <v>143.88</v>
+      </c>
+      <c r="M165" t="n">
+        <v>195.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M165"/>
+  <dimension ref="A1:M166"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6547,6 +6547,43 @@
         <v>195.49</v>
       </c>
     </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>1736.84</v>
+      </c>
+      <c r="D166" t="n">
+        <v>1479016.83</v>
+      </c>
+      <c r="E166" t="n">
+        <v>263.24</v>
+      </c>
+      <c r="F166" t="n">
+        <v>159.85</v>
+      </c>
+      <c r="G166" t="n">
+        <v>269.29</v>
+      </c>
+      <c r="H166" t="n">
+        <v>1690</v>
+      </c>
+      <c r="J166" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K166" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="L166" t="n">
+        <v>144.99</v>
+      </c>
+      <c r="M166" t="n">
+        <v>195.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M166"/>
+  <dimension ref="A1:M167"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6584,6 +6584,43 @@
         <v>195.49</v>
       </c>
     </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>1739.81</v>
+      </c>
+      <c r="D167" t="n">
+        <v>1479016.83</v>
+      </c>
+      <c r="E167" t="n">
+        <v>261.39</v>
+      </c>
+      <c r="F167" t="n">
+        <v>164.46</v>
+      </c>
+      <c r="G167" t="n">
+        <v>269.49</v>
+      </c>
+      <c r="H167" t="n">
+        <v>1690</v>
+      </c>
+      <c r="J167" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K167" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="L167" t="n">
+        <v>157.31</v>
+      </c>
+      <c r="M167" t="n">
+        <v>197.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M167"/>
+  <dimension ref="A1:M168"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6621,6 +6621,43 @@
         <v>197.49</v>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>1739.81</v>
+      </c>
+      <c r="D168" t="n">
+        <v>1479016.83</v>
+      </c>
+      <c r="E168" t="n">
+        <v>293.79</v>
+      </c>
+      <c r="F168" t="n">
+        <v>152.74</v>
+      </c>
+      <c r="G168" t="n">
+        <v>269.49</v>
+      </c>
+      <c r="H168" t="n">
+        <v>1690</v>
+      </c>
+      <c r="J168" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K168" t="n">
+        <v>130.78</v>
+      </c>
+      <c r="L168" t="n">
+        <v>147.37</v>
+      </c>
+      <c r="M168" t="n">
+        <v>197.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M168"/>
+  <dimension ref="A1:M169"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6658,6 +6658,43 @@
         <v>197.49</v>
       </c>
     </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>1739.81</v>
+      </c>
+      <c r="D169" t="n">
+        <v>1479016.83</v>
+      </c>
+      <c r="E169" t="n">
+        <v>285.63</v>
+      </c>
+      <c r="F169" t="n">
+        <v>160.9</v>
+      </c>
+      <c r="G169" t="n">
+        <v>243.74</v>
+      </c>
+      <c r="H169" t="n">
+        <v>1690</v>
+      </c>
+      <c r="J169" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K169" t="n">
+        <v>130.94</v>
+      </c>
+      <c r="L169" t="n">
+        <v>148.48</v>
+      </c>
+      <c r="M169" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M169"/>
+  <dimension ref="A1:M170"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6695,6 +6695,43 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>1739.81</v>
+      </c>
+      <c r="D170" t="n">
+        <v>1479016.83</v>
+      </c>
+      <c r="E170" t="n">
+        <v>276.6</v>
+      </c>
+      <c r="F170" t="n">
+        <v>134.88</v>
+      </c>
+      <c r="G170" t="n">
+        <v>243.92</v>
+      </c>
+      <c r="H170" t="n">
+        <v>1690</v>
+      </c>
+      <c r="J170" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K170" t="n">
+        <v>130.61</v>
+      </c>
+      <c r="L170" t="n">
+        <v>144.45</v>
+      </c>
+      <c r="M170" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M170"/>
+  <dimension ref="A1:M171"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6732,6 +6732,43 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>1739.81</v>
+      </c>
+      <c r="D171" t="n">
+        <v>1479016.83</v>
+      </c>
+      <c r="E171" t="n">
+        <v>261.98</v>
+      </c>
+      <c r="F171" t="n">
+        <v>131.45</v>
+      </c>
+      <c r="G171" t="n">
+        <v>243.42</v>
+      </c>
+      <c r="H171" t="n">
+        <v>1690</v>
+      </c>
+      <c r="J171" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K171" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="L171" t="n">
+        <v>140.21</v>
+      </c>
+      <c r="M171" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M171"/>
+  <dimension ref="A1:M172"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6769,6 +6769,43 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>1739.81</v>
+      </c>
+      <c r="D172" t="n">
+        <v>1479016.83</v>
+      </c>
+      <c r="E172" t="n">
+        <v>261.98</v>
+      </c>
+      <c r="F172" t="n">
+        <v>127.03</v>
+      </c>
+      <c r="G172" t="n">
+        <v>243.82</v>
+      </c>
+      <c r="H172" t="n">
+        <v>1690</v>
+      </c>
+      <c r="J172" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K172" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="L172" t="n">
+        <v>132.71</v>
+      </c>
+      <c r="M172" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M172"/>
+  <dimension ref="A1:M173"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6806,6 +6806,43 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>1739.81</v>
+      </c>
+      <c r="D173" t="n">
+        <v>1479016.83</v>
+      </c>
+      <c r="E173" t="n">
+        <v>261.98</v>
+      </c>
+      <c r="F173" t="n">
+        <v>162.06</v>
+      </c>
+      <c r="G173" t="n">
+        <v>243.82</v>
+      </c>
+      <c r="H173" t="n">
+        <v>1690</v>
+      </c>
+      <c r="J173" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K173" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="L173" t="n">
+        <v>144.44</v>
+      </c>
+      <c r="M173" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M173"/>
+  <dimension ref="A1:M174"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6843,6 +6843,43 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>1739.81</v>
+      </c>
+      <c r="D174" t="n">
+        <v>1479016.83</v>
+      </c>
+      <c r="E174" t="n">
+        <v>265.68</v>
+      </c>
+      <c r="F174" t="n">
+        <v>158.32</v>
+      </c>
+      <c r="G174" t="n">
+        <v>243.82</v>
+      </c>
+      <c r="H174" t="n">
+        <v>1690</v>
+      </c>
+      <c r="J174" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K174" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="L174" t="n">
+        <v>149</v>
+      </c>
+      <c r="M174" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M174"/>
+  <dimension ref="A1:M175"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6880,6 +6880,43 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>1739.81</v>
+      </c>
+      <c r="D175" t="n">
+        <v>1435538.57</v>
+      </c>
+      <c r="E175" t="n">
+        <v>260.58</v>
+      </c>
+      <c r="F175" t="n">
+        <v>129.28</v>
+      </c>
+      <c r="G175" t="n">
+        <v>243.83</v>
+      </c>
+      <c r="H175" t="n">
+        <v>1690</v>
+      </c>
+      <c r="J175" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K175" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="L175" t="n">
+        <v>132.08</v>
+      </c>
+      <c r="M175" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M175"/>
+  <dimension ref="A1:M176"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6917,6 +6917,43 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>128.84</v>
+      </c>
+      <c r="D176" t="n">
+        <v>1435538.57</v>
+      </c>
+      <c r="E176" t="n">
+        <v>279.4</v>
+      </c>
+      <c r="F176" t="n">
+        <v>134.45</v>
+      </c>
+      <c r="G176" t="n">
+        <v>236.19</v>
+      </c>
+      <c r="I176" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="J176" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K176" t="n">
+        <v>130.61</v>
+      </c>
+      <c r="L176" t="n">
+        <v>140.18</v>
+      </c>
+      <c r="M176" t="n">
+        <v>175.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M176"/>
+  <dimension ref="A1:M177"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6954,6 +6954,37 @@
         <v>175.49</v>
       </c>
     </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>1435538.57</v>
+      </c>
+      <c r="E177" t="n">
+        <v>245.86</v>
+      </c>
+      <c r="F177" t="n">
+        <v>132.01</v>
+      </c>
+      <c r="G177" t="n">
+        <v>287.79</v>
+      </c>
+      <c r="J177" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K177" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="L177" t="n">
+        <v>140.24</v>
+      </c>
+      <c r="M177" t="n">
+        <v>197.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M177"/>
+  <dimension ref="A1:M178"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6985,6 +6985,37 @@
         <v>197.49</v>
       </c>
     </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>1435538.57</v>
+      </c>
+      <c r="E178" t="n">
+        <v>247.38</v>
+      </c>
+      <c r="F178" t="n">
+        <v>131.53</v>
+      </c>
+      <c r="G178" t="n">
+        <v>287.79</v>
+      </c>
+      <c r="J178" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K178" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="L178" t="n">
+        <v>138.1</v>
+      </c>
+      <c r="M178" t="n">
+        <v>197.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M178"/>
+  <dimension ref="A1:M179"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7016,6 +7016,37 @@
         <v>197.49</v>
       </c>
     </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>1435538.57</v>
+      </c>
+      <c r="E179" t="n">
+        <v>247.38</v>
+      </c>
+      <c r="F179" t="n">
+        <v>135.5</v>
+      </c>
+      <c r="G179" t="n">
+        <v>287.79</v>
+      </c>
+      <c r="J179" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K179" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="L179" t="n">
+        <v>141.28</v>
+      </c>
+      <c r="M179" t="n">
+        <v>197.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M179"/>
+  <dimension ref="A1:M180"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7047,6 +7047,37 @@
         <v>197.49</v>
       </c>
     </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>1602.86</v>
+      </c>
+      <c r="E180" t="n">
+        <v>247.38</v>
+      </c>
+      <c r="F180" t="n">
+        <v>131.65</v>
+      </c>
+      <c r="G180" t="n">
+        <v>287.79</v>
+      </c>
+      <c r="J180" t="n">
+        <v>1599</v>
+      </c>
+      <c r="K180" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="L180" t="n">
+        <v>134.99</v>
+      </c>
+      <c r="M180" t="n">
+        <v>197.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M180"/>
+  <dimension ref="A1:M181"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7078,6 +7078,37 @@
         <v>197.49</v>
       </c>
     </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>1602.86</v>
+      </c>
+      <c r="E181" t="n">
+        <v>246.91</v>
+      </c>
+      <c r="F181" t="n">
+        <v>132.7</v>
+      </c>
+      <c r="G181" t="n">
+        <v>287.79</v>
+      </c>
+      <c r="J181" t="n">
+        <v>1599</v>
+      </c>
+      <c r="K181" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="L181" t="n">
+        <v>140.53</v>
+      </c>
+      <c r="M181" t="n">
+        <v>197.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M181"/>
+  <dimension ref="A1:M182"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7109,6 +7109,37 @@
         <v>197.49</v>
       </c>
     </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>1602.86</v>
+      </c>
+      <c r="E182" t="n">
+        <v>253.75</v>
+      </c>
+      <c r="F182" t="n">
+        <v>134.35</v>
+      </c>
+      <c r="G182" t="n">
+        <v>287.79</v>
+      </c>
+      <c r="J182" t="n">
+        <v>1599</v>
+      </c>
+      <c r="K182" t="n">
+        <v>130.78</v>
+      </c>
+      <c r="L182" t="n">
+        <v>140.18</v>
+      </c>
+      <c r="M182" t="n">
+        <v>197.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M182"/>
+  <dimension ref="A1:M183"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7140,6 +7140,37 @@
         <v>197.49</v>
       </c>
     </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>857643.39</v>
+      </c>
+      <c r="E183" t="n">
+        <v>257.16</v>
+      </c>
+      <c r="F183" t="n">
+        <v>141.18</v>
+      </c>
+      <c r="G183" t="n">
+        <v>294.39</v>
+      </c>
+      <c r="J183" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K183" t="n">
+        <v>130.78</v>
+      </c>
+      <c r="L183" t="n">
+        <v>145.86</v>
+      </c>
+      <c r="M183" t="n">
+        <v>197.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M183"/>
+  <dimension ref="A1:M184"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7171,6 +7171,37 @@
         <v>197.49</v>
       </c>
     </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>857643.39</v>
+      </c>
+      <c r="E184" t="n">
+        <v>264.65</v>
+      </c>
+      <c r="F184" t="n">
+        <v>137.77</v>
+      </c>
+      <c r="G184" t="n">
+        <v>294.39</v>
+      </c>
+      <c r="J184" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K184" t="n">
+        <v>130.95</v>
+      </c>
+      <c r="L184" t="n">
+        <v>147.05</v>
+      </c>
+      <c r="M184" t="n">
+        <v>197.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M184"/>
+  <dimension ref="A1:M185"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7202,6 +7202,37 @@
         <v>197.49</v>
       </c>
     </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>857643.39</v>
+      </c>
+      <c r="E185" t="n">
+        <v>263.85</v>
+      </c>
+      <c r="F185" t="n">
+        <v>139.74</v>
+      </c>
+      <c r="G185" t="n">
+        <v>294.39</v>
+      </c>
+      <c r="J185" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K185" t="n">
+        <v>135.97</v>
+      </c>
+      <c r="L185" t="n">
+        <v>145.86</v>
+      </c>
+      <c r="M185" t="n">
+        <v>197.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M185"/>
+  <dimension ref="A1:M186"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7233,6 +7233,37 @@
         <v>197.49</v>
       </c>
     </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>857643.39</v>
+      </c>
+      <c r="E186" t="n">
+        <v>263.85</v>
+      </c>
+      <c r="F186" t="n">
+        <v>140.53</v>
+      </c>
+      <c r="G186" t="n">
+        <v>294.39</v>
+      </c>
+      <c r="J186" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K186" t="n">
+        <v>135.97</v>
+      </c>
+      <c r="L186" t="n">
+        <v>149.81</v>
+      </c>
+      <c r="M186" t="n">
+        <v>197.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M186"/>
+  <dimension ref="A1:M187"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7264,6 +7264,37 @@
         <v>197.49</v>
       </c>
     </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>857643.39</v>
+      </c>
+      <c r="E187" t="n">
+        <v>263.85</v>
+      </c>
+      <c r="F187" t="n">
+        <v>139.86</v>
+      </c>
+      <c r="G187" t="n">
+        <v>294.39</v>
+      </c>
+      <c r="J187" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K187" t="n">
+        <v>135.97</v>
+      </c>
+      <c r="L187" t="n">
+        <v>146.46</v>
+      </c>
+      <c r="M187" t="n">
+        <v>197.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M187"/>
+  <dimension ref="A1:M188"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7295,6 +7295,37 @@
         <v>197.49</v>
       </c>
     </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>857643.39</v>
+      </c>
+      <c r="E188" t="n">
+        <v>263.85</v>
+      </c>
+      <c r="F188" t="n">
+        <v>138.24</v>
+      </c>
+      <c r="G188" t="n">
+        <v>258.94</v>
+      </c>
+      <c r="J188" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K188" t="n">
+        <v>135.97</v>
+      </c>
+      <c r="L188" t="n">
+        <v>151.58</v>
+      </c>
+      <c r="M188" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M188"/>
+  <dimension ref="A1:M189"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7326,6 +7326,37 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>857643.39</v>
+      </c>
+      <c r="E189" t="n">
+        <v>263.85</v>
+      </c>
+      <c r="F189" t="n">
+        <v>141.77</v>
+      </c>
+      <c r="G189" t="n">
+        <v>258.94</v>
+      </c>
+      <c r="J189" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K189" t="n">
+        <v>135.97</v>
+      </c>
+      <c r="L189" t="n">
+        <v>147.92</v>
+      </c>
+      <c r="M189" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M189"/>
+  <dimension ref="A1:M190"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7357,6 +7357,37 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>821999.88</v>
+      </c>
+      <c r="E190" t="n">
+        <v>346.88</v>
+      </c>
+      <c r="F190" t="n">
+        <v>140.47</v>
+      </c>
+      <c r="G190" t="n">
+        <v>258.94</v>
+      </c>
+      <c r="J190" t="n">
+        <v>1790</v>
+      </c>
+      <c r="K190" t="n">
+        <v>140.49</v>
+      </c>
+      <c r="L190" t="n">
+        <v>147.49</v>
+      </c>
+      <c r="M190" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M190"/>
+  <dimension ref="A1:M191"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7388,6 +7388,37 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>821938.58</v>
+      </c>
+      <c r="E191" t="n">
+        <v>308.77</v>
+      </c>
+      <c r="F191" t="n">
+        <v>140.9</v>
+      </c>
+      <c r="G191" t="n">
+        <v>258.94</v>
+      </c>
+      <c r="J191" t="n">
+        <v>1539</v>
+      </c>
+      <c r="K191" t="n">
+        <v>139.99</v>
+      </c>
+      <c r="L191" t="n">
+        <v>147.4</v>
+      </c>
+      <c r="M191" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M191"/>
+  <dimension ref="A1:M192"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7419,6 +7419,37 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>821911.92</v>
+      </c>
+      <c r="E192" t="n">
+        <v>308.97</v>
+      </c>
+      <c r="F192" t="n">
+        <v>135</v>
+      </c>
+      <c r="G192" t="n">
+        <v>258.94</v>
+      </c>
+      <c r="J192" t="n">
+        <v>1539</v>
+      </c>
+      <c r="K192" t="n">
+        <v>140.99</v>
+      </c>
+      <c r="L192" t="n">
+        <v>137.36</v>
+      </c>
+      <c r="M192" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M192"/>
+  <dimension ref="A1:M193"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7450,6 +7450,37 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>821911.92</v>
+      </c>
+      <c r="E193" t="n">
+        <v>299.19</v>
+      </c>
+      <c r="F193" t="n">
+        <v>141.34</v>
+      </c>
+      <c r="G193" t="n">
+        <v>258.94</v>
+      </c>
+      <c r="J193" t="n">
+        <v>1539</v>
+      </c>
+      <c r="K193" t="n">
+        <v>130.94</v>
+      </c>
+      <c r="L193" t="n">
+        <v>147.92</v>
+      </c>
+      <c r="M193" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M193"/>
+  <dimension ref="A1:M194"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7481,6 +7481,37 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>821911.92</v>
+      </c>
+      <c r="E194" t="n">
+        <v>299.19</v>
+      </c>
+      <c r="F194" t="n">
+        <v>138.77</v>
+      </c>
+      <c r="G194" t="n">
+        <v>258.94</v>
+      </c>
+      <c r="J194" t="n">
+        <v>1539</v>
+      </c>
+      <c r="K194" t="n">
+        <v>130.94</v>
+      </c>
+      <c r="L194" t="n">
+        <v>144.3</v>
+      </c>
+      <c r="M194" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M194"/>
+  <dimension ref="A1:M195"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7512,6 +7512,37 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>821911.92</v>
+      </c>
+      <c r="E195" t="n">
+        <v>299.19</v>
+      </c>
+      <c r="F195" t="n">
+        <v>132.6</v>
+      </c>
+      <c r="G195" t="n">
+        <v>258.94</v>
+      </c>
+      <c r="J195" t="n">
+        <v>1539</v>
+      </c>
+      <c r="K195" t="n">
+        <v>130.94</v>
+      </c>
+      <c r="L195" t="n">
+        <v>140.91</v>
+      </c>
+      <c r="M195" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M195"/>
+  <dimension ref="A1:M196"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7543,6 +7543,43 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>131.55</v>
+      </c>
+      <c r="D196" t="n">
+        <v>33249.45</v>
+      </c>
+      <c r="E196" t="n">
+        <v>299.19</v>
+      </c>
+      <c r="F196" t="n">
+        <v>137.74</v>
+      </c>
+      <c r="G196" t="n">
+        <v>258.94</v>
+      </c>
+      <c r="I196" t="n">
+        <v>131.99</v>
+      </c>
+      <c r="J196" t="n">
+        <v>1484</v>
+      </c>
+      <c r="K196" t="n">
+        <v>130.94</v>
+      </c>
+      <c r="L196" t="n">
+        <v>136.31</v>
+      </c>
+      <c r="M196" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M196"/>
+  <dimension ref="A1:M197"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7580,6 +7580,37 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>33249.45</v>
+      </c>
+      <c r="E197" t="n">
+        <v>308.48</v>
+      </c>
+      <c r="F197" t="n">
+        <v>137.55</v>
+      </c>
+      <c r="G197" t="n">
+        <v>258.94</v>
+      </c>
+      <c r="J197" t="n">
+        <v>1484</v>
+      </c>
+      <c r="K197" t="n">
+        <v>131.47</v>
+      </c>
+      <c r="L197" t="n">
+        <v>134.99</v>
+      </c>
+      <c r="M197" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M197"/>
+  <dimension ref="A1:M198"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7611,6 +7611,37 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>31873.09</v>
+      </c>
+      <c r="E198" t="n">
+        <v>429.77</v>
+      </c>
+      <c r="F198" t="n">
+        <v>134.52</v>
+      </c>
+      <c r="G198" t="n">
+        <v>258.94</v>
+      </c>
+      <c r="J198" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K198" t="n">
+        <v>140.99</v>
+      </c>
+      <c r="L198" t="n">
+        <v>143.71</v>
+      </c>
+      <c r="M198" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M198"/>
+  <dimension ref="A1:M199"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7642,6 +7642,37 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>31873.09</v>
+      </c>
+      <c r="E199" t="n">
+        <v>311.27</v>
+      </c>
+      <c r="F199" t="n">
+        <v>130.07</v>
+      </c>
+      <c r="G199" t="n">
+        <v>258.94</v>
+      </c>
+      <c r="J199" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K199" t="n">
+        <v>130.94</v>
+      </c>
+      <c r="L199" t="n">
+        <v>143.27</v>
+      </c>
+      <c r="M199" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M199"/>
+  <dimension ref="A1:M200"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7673,6 +7673,37 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>31873.09</v>
+      </c>
+      <c r="E200" t="n">
+        <v>268.29</v>
+      </c>
+      <c r="F200" t="n">
+        <v>127.67</v>
+      </c>
+      <c r="G200" t="n">
+        <v>258.94</v>
+      </c>
+      <c r="J200" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K200" t="n">
+        <v>130.61</v>
+      </c>
+      <c r="L200" t="n">
+        <v>131.58</v>
+      </c>
+      <c r="M200" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M200"/>
+  <dimension ref="A1:M201"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7704,6 +7704,37 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>31873.09</v>
+      </c>
+      <c r="E201" t="n">
+        <v>486.49</v>
+      </c>
+      <c r="F201" t="n">
+        <v>134.94</v>
+      </c>
+      <c r="G201" t="n">
+        <v>258.94</v>
+      </c>
+      <c r="J201" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K201" t="n">
+        <v>130.95</v>
+      </c>
+      <c r="L201" t="n">
+        <v>143.32</v>
+      </c>
+      <c r="M201" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M201"/>
+  <dimension ref="A1:M202"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7735,6 +7735,37 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>31884.83</v>
+      </c>
+      <c r="E202" t="n">
+        <v>486.49</v>
+      </c>
+      <c r="F202" t="n">
+        <v>134.64</v>
+      </c>
+      <c r="G202" t="n">
+        <v>258.94</v>
+      </c>
+      <c r="J202" t="n">
+        <v>1559</v>
+      </c>
+      <c r="K202" t="n">
+        <v>130.95</v>
+      </c>
+      <c r="L202" t="n">
+        <v>136.98</v>
+      </c>
+      <c r="M202" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M202"/>
+  <dimension ref="A1:M203"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7766,6 +7766,37 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>31884.83</v>
+      </c>
+      <c r="E203" t="n">
+        <v>531.7</v>
+      </c>
+      <c r="F203" t="n">
+        <v>132.02</v>
+      </c>
+      <c r="G203" t="n">
+        <v>266.99</v>
+      </c>
+      <c r="J203" t="n">
+        <v>1559</v>
+      </c>
+      <c r="K203" t="n">
+        <v>147.93</v>
+      </c>
+      <c r="L203" t="n">
+        <v>136.4</v>
+      </c>
+      <c r="M203" t="n">
+        <v>197.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M203"/>
+  <dimension ref="A1:M204"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7797,6 +7797,37 @@
         <v>197.49</v>
       </c>
     </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>31881.83</v>
+      </c>
+      <c r="E204" t="n">
+        <v>448.81</v>
+      </c>
+      <c r="F204" t="n">
+        <v>137.66</v>
+      </c>
+      <c r="G204" t="n">
+        <v>266.99</v>
+      </c>
+      <c r="J204" t="n">
+        <v>1559</v>
+      </c>
+      <c r="K204" t="n">
+        <v>130.94</v>
+      </c>
+      <c r="L204" t="n">
+        <v>138.32</v>
+      </c>
+      <c r="M204" t="n">
+        <v>197.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M204"/>
+  <dimension ref="A1:M205"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7828,6 +7828,37 @@
         <v>197.49</v>
       </c>
     </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>31881.83</v>
+      </c>
+      <c r="E205" t="n">
+        <v>305.25</v>
+      </c>
+      <c r="F205" t="n">
+        <v>135.92</v>
+      </c>
+      <c r="G205" t="n">
+        <v>266.99</v>
+      </c>
+      <c r="J205" t="n">
+        <v>1559</v>
+      </c>
+      <c r="K205" t="n">
+        <v>150.87</v>
+      </c>
+      <c r="L205" t="n">
+        <v>136.4</v>
+      </c>
+      <c r="M205" t="n">
+        <v>197.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M205"/>
+  <dimension ref="A1:M206"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7859,6 +7859,37 @@
         <v>197.49</v>
       </c>
     </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>31881.83</v>
+      </c>
+      <c r="E206" t="n">
+        <v>307.66</v>
+      </c>
+      <c r="F206" t="n">
+        <v>132.06</v>
+      </c>
+      <c r="G206" t="n">
+        <v>266.99</v>
+      </c>
+      <c r="J206" t="n">
+        <v>1559</v>
+      </c>
+      <c r="K206" t="n">
+        <v>147.93</v>
+      </c>
+      <c r="L206" t="n">
+        <v>135.75</v>
+      </c>
+      <c r="M206" t="n">
+        <v>197.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M206"/>
+  <dimension ref="A1:M207"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7890,6 +7890,37 @@
         <v>197.49</v>
       </c>
     </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>31881.83</v>
+      </c>
+      <c r="E207" t="n">
+        <v>317.27</v>
+      </c>
+      <c r="F207" t="n">
+        <v>131.77</v>
+      </c>
+      <c r="G207" t="n">
+        <v>261.24</v>
+      </c>
+      <c r="J207" t="n">
+        <v>1559</v>
+      </c>
+      <c r="K207" t="n">
+        <v>150.87</v>
+      </c>
+      <c r="L207" t="n">
+        <v>136.54</v>
+      </c>
+      <c r="M207" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M207"/>
+  <dimension ref="A1:M208"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7921,6 +7921,37 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>31881.83</v>
+      </c>
+      <c r="E208" t="n">
+        <v>317.27</v>
+      </c>
+      <c r="F208" t="n">
+        <v>133.56</v>
+      </c>
+      <c r="G208" t="n">
+        <v>261.24</v>
+      </c>
+      <c r="J208" t="n">
+        <v>1559</v>
+      </c>
+      <c r="K208" t="n">
+        <v>150.87</v>
+      </c>
+      <c r="L208" t="n">
+        <v>137.19</v>
+      </c>
+      <c r="M208" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M208"/>
+  <dimension ref="A1:M209"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7952,6 +7952,43 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>162.65</v>
+      </c>
+      <c r="D209" t="n">
+        <v>31881.83</v>
+      </c>
+      <c r="E209" t="n">
+        <v>317.27</v>
+      </c>
+      <c r="F209" t="n">
+        <v>137.33</v>
+      </c>
+      <c r="G209" t="n">
+        <v>261.99</v>
+      </c>
+      <c r="I209" t="n">
+        <v>159.99</v>
+      </c>
+      <c r="J209" t="n">
+        <v>1559</v>
+      </c>
+      <c r="K209" t="n">
+        <v>150.87</v>
+      </c>
+      <c r="L209" t="n">
+        <v>143.55</v>
+      </c>
+      <c r="M209" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M209"/>
+  <dimension ref="A1:M210"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7989,6 +7989,37 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>1504.68</v>
+      </c>
+      <c r="E210" t="n">
+        <v>263.74</v>
+      </c>
+      <c r="F210" t="n">
+        <v>140.06</v>
+      </c>
+      <c r="G210" t="n">
+        <v>266.99</v>
+      </c>
+      <c r="J210" t="n">
+        <v>1539</v>
+      </c>
+      <c r="K210" t="n">
+        <v>140.99</v>
+      </c>
+      <c r="L210" t="n">
+        <v>144.8</v>
+      </c>
+      <c r="M210" t="n">
+        <v>197.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M210"/>
+  <dimension ref="A1:M211"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8020,6 +8020,37 @@
         <v>197.49</v>
       </c>
     </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>1502.1</v>
+      </c>
+      <c r="E211" t="n">
+        <v>394.74</v>
+      </c>
+      <c r="F211" t="n">
+        <v>138.57</v>
+      </c>
+      <c r="G211" t="n">
+        <v>266.99</v>
+      </c>
+      <c r="J211" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K211" t="n">
+        <v>135.97</v>
+      </c>
+      <c r="L211" t="n">
+        <v>137.72</v>
+      </c>
+      <c r="M211" t="n">
+        <v>197.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M211"/>
+  <dimension ref="A1:M212"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8051,6 +8051,43 @@
         <v>197.49</v>
       </c>
     </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>164.62</v>
+      </c>
+      <c r="D212" t="n">
+        <v>1502.1</v>
+      </c>
+      <c r="E212" t="n">
+        <v>263.71</v>
+      </c>
+      <c r="F212" t="n">
+        <v>140.15</v>
+      </c>
+      <c r="G212" t="n">
+        <v>266.99</v>
+      </c>
+      <c r="I212" t="n">
+        <v>154.99</v>
+      </c>
+      <c r="J212" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K212" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="L212" t="n">
+        <v>139.87</v>
+      </c>
+      <c r="M212" t="n">
+        <v>197.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M212"/>
+  <dimension ref="A1:M213"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8088,6 +8088,37 @@
         <v>197.49</v>
       </c>
     </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>1502.1</v>
+      </c>
+      <c r="E213" t="n">
+        <v>261.26</v>
+      </c>
+      <c r="F213" t="n">
+        <v>138.49</v>
+      </c>
+      <c r="G213" t="n">
+        <v>266.99</v>
+      </c>
+      <c r="J213" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K213" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="L213" t="n">
+        <v>137.12</v>
+      </c>
+      <c r="M213" t="n">
+        <v>197.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M213"/>
+  <dimension ref="A1:M214"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8119,6 +8119,37 @@
         <v>197.49</v>
       </c>
     </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>1502.1</v>
+      </c>
+      <c r="E214" t="n">
+        <v>273.73</v>
+      </c>
+      <c r="F214" t="n">
+        <v>138.56</v>
+      </c>
+      <c r="G214" t="n">
+        <v>266.99</v>
+      </c>
+      <c r="J214" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K214" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="L214" t="n">
+        <v>140.24</v>
+      </c>
+      <c r="M214" t="n">
+        <v>197.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M214"/>
+  <dimension ref="A1:M215"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8150,6 +8150,37 @@
         <v>197.49</v>
       </c>
     </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>1502.1</v>
+      </c>
+      <c r="E215" t="n">
+        <v>273.73</v>
+      </c>
+      <c r="F215" t="n">
+        <v>134.24</v>
+      </c>
+      <c r="G215" t="n">
+        <v>266.99</v>
+      </c>
+      <c r="J215" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K215" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="L215" t="n">
+        <v>122.61</v>
+      </c>
+      <c r="M215" t="n">
+        <v>197.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M215"/>
+  <dimension ref="A1:M216"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8181,6 +8181,37 @@
         <v>197.49</v>
       </c>
     </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>1502.1</v>
+      </c>
+      <c r="E216" t="n">
+        <v>273.73</v>
+      </c>
+      <c r="F216" t="n">
+        <v>139.85</v>
+      </c>
+      <c r="G216" t="n">
+        <v>266.99</v>
+      </c>
+      <c r="J216" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K216" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="L216" t="n">
+        <v>144.01</v>
+      </c>
+      <c r="M216" t="n">
+        <v>197.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M216"/>
+  <dimension ref="A1:M217"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8212,6 +8212,37 @@
         <v>197.49</v>
       </c>
     </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>1502.1</v>
+      </c>
+      <c r="E217" t="n">
+        <v>273.73</v>
+      </c>
+      <c r="F217" t="n">
+        <v>135.86</v>
+      </c>
+      <c r="G217" t="n">
+        <v>243.64</v>
+      </c>
+      <c r="J217" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K217" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="L217" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="M217" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M217"/>
+  <dimension ref="A1:M218"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8243,6 +8243,37 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>1502.1</v>
+      </c>
+      <c r="E218" t="n">
+        <v>294.78</v>
+      </c>
+      <c r="F218" t="n">
+        <v>135.45</v>
+      </c>
+      <c r="G218" t="n">
+        <v>243.64</v>
+      </c>
+      <c r="J218" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K218" t="n">
+        <v>130.3</v>
+      </c>
+      <c r="L218" t="n">
+        <v>134.37</v>
+      </c>
+      <c r="M218" t="n">
+        <v>194.98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M218"/>
+  <dimension ref="A1:M219"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8274,6 +8274,31 @@
         <v>194.98</v>
       </c>
     </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>1502.1</v>
+      </c>
+      <c r="F219" t="n">
+        <v>133.03</v>
+      </c>
+      <c r="G219" t="n">
+        <v>243.64</v>
+      </c>
+      <c r="J219" t="n">
+        <v>1519</v>
+      </c>
+      <c r="L219" t="n">
+        <v>128.61</v>
+      </c>
+      <c r="M219" t="n">
+        <v>194.98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M219"/>
+  <dimension ref="A1:M220"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8299,6 +8299,37 @@
         <v>194.98</v>
       </c>
     </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>1515.59</v>
+      </c>
+      <c r="E220" t="n">
+        <v>284.47</v>
+      </c>
+      <c r="F220" t="n">
+        <v>126.59</v>
+      </c>
+      <c r="G220" t="n">
+        <v>243.64</v>
+      </c>
+      <c r="J220" t="n">
+        <v>1539</v>
+      </c>
+      <c r="K220" t="n">
+        <v>130.78</v>
+      </c>
+      <c r="L220" t="n">
+        <v>122.61</v>
+      </c>
+      <c r="M220" t="n">
+        <v>194.98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M220"/>
+  <dimension ref="A1:M221"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8330,6 +8330,37 @@
         <v>194.98</v>
       </c>
     </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>1515.59</v>
+      </c>
+      <c r="E221" t="n">
+        <v>284.47</v>
+      </c>
+      <c r="F221" t="n">
+        <v>134.69</v>
+      </c>
+      <c r="G221" t="n">
+        <v>243.64</v>
+      </c>
+      <c r="J221" t="n">
+        <v>1539</v>
+      </c>
+      <c r="K221" t="n">
+        <v>130.78</v>
+      </c>
+      <c r="L221" t="n">
+        <v>131.51</v>
+      </c>
+      <c r="M221" t="n">
+        <v>194.98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M221"/>
+  <dimension ref="A1:M222"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8361,6 +8361,37 @@
         <v>194.98</v>
       </c>
     </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>1515.59</v>
+      </c>
+      <c r="E222" t="n">
+        <v>284.47</v>
+      </c>
+      <c r="F222" t="n">
+        <v>134.26</v>
+      </c>
+      <c r="G222" t="n">
+        <v>243.64</v>
+      </c>
+      <c r="J222" t="n">
+        <v>1539</v>
+      </c>
+      <c r="K222" t="n">
+        <v>130.78</v>
+      </c>
+      <c r="L222" t="n">
+        <v>133.04</v>
+      </c>
+      <c r="M222" t="n">
+        <v>194.98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M222"/>
+  <dimension ref="A1:M223"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8392,6 +8392,37 @@
         <v>194.98</v>
       </c>
     </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>1515.59</v>
+      </c>
+      <c r="E223" t="n">
+        <v>262.8</v>
+      </c>
+      <c r="F223" t="n">
+        <v>137.59</v>
+      </c>
+      <c r="G223" t="n">
+        <v>243.64</v>
+      </c>
+      <c r="J223" t="n">
+        <v>1539</v>
+      </c>
+      <c r="K223" t="n">
+        <v>130.3</v>
+      </c>
+      <c r="L223" t="n">
+        <v>135.37</v>
+      </c>
+      <c r="M223" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M223"/>
+  <dimension ref="A1:M224"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8423,6 +8423,37 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>1449.68</v>
+      </c>
+      <c r="E224" t="n">
+        <v>288.4</v>
+      </c>
+      <c r="F224" t="n">
+        <v>135.95</v>
+      </c>
+      <c r="G224" t="n">
+        <v>243.64</v>
+      </c>
+      <c r="J224" t="n">
+        <v>1509</v>
+      </c>
+      <c r="K224" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="L224" t="n">
+        <v>134.82</v>
+      </c>
+      <c r="M224" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M224"/>
+  <dimension ref="A1:M225"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8454,6 +8454,37 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>435802.26</v>
+      </c>
+      <c r="E225" t="n">
+        <v>288.4</v>
+      </c>
+      <c r="F225" t="n">
+        <v>141.65</v>
+      </c>
+      <c r="G225" t="n">
+        <v>243.39</v>
+      </c>
+      <c r="J225" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K225" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="L225" t="n">
+        <v>150.74</v>
+      </c>
+      <c r="M225" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M225"/>
+  <dimension ref="A1:M226"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8485,6 +8485,37 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>435802.26</v>
+      </c>
+      <c r="E226" t="n">
+        <v>307.25</v>
+      </c>
+      <c r="F226" t="n">
+        <v>127.89</v>
+      </c>
+      <c r="G226" t="n">
+        <v>243.39</v>
+      </c>
+      <c r="J226" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K226" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="L226" t="n">
+        <v>120.06</v>
+      </c>
+      <c r="M226" t="n">
+        <v>194.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M226"/>
+  <dimension ref="A1:M227"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8516,6 +8516,43 @@
         <v>194.99</v>
       </c>
     </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>159.88</v>
+      </c>
+      <c r="D227" t="n">
+        <v>455571.05</v>
+      </c>
+      <c r="E227" t="n">
+        <v>307.25</v>
+      </c>
+      <c r="F227" t="n">
+        <v>121.11</v>
+      </c>
+      <c r="G227" t="n">
+        <v>138.34</v>
+      </c>
+      <c r="I227" t="n">
+        <v>159.99</v>
+      </c>
+      <c r="J227" t="n">
+        <v>1539</v>
+      </c>
+      <c r="K227" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="L227" t="n">
+        <v>112.73</v>
+      </c>
+      <c r="M227" t="n">
+        <v>144.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M227"/>
+  <dimension ref="A1:M228"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8553,6 +8553,43 @@
         <v>144.99</v>
       </c>
     </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>164.62</v>
+      </c>
+      <c r="D228" t="n">
+        <v>435802.26</v>
+      </c>
+      <c r="E228" t="n">
+        <v>307.25</v>
+      </c>
+      <c r="F228" t="n">
+        <v>127.01</v>
+      </c>
+      <c r="G228" t="n">
+        <v>138.34</v>
+      </c>
+      <c r="I228" t="n">
+        <v>164.99</v>
+      </c>
+      <c r="J228" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K228" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="L228" t="n">
+        <v>120.02</v>
+      </c>
+      <c r="M228" t="n">
+        <v>144.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M228"/>
+  <dimension ref="A1:M229"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8590,6 +8590,37 @@
         <v>144.99</v>
       </c>
     </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>435802.26</v>
+      </c>
+      <c r="E229" t="n">
+        <v>307.25</v>
+      </c>
+      <c r="F229" t="n">
+        <v>118.04</v>
+      </c>
+      <c r="G229" t="n">
+        <v>133.36</v>
+      </c>
+      <c r="J229" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K229" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="L229" t="n">
+        <v>107.78</v>
+      </c>
+      <c r="M229" t="n">
+        <v>134.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M229"/>
+  <dimension ref="A1:M230"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8621,6 +8621,43 @@
         <v>134.99</v>
       </c>
     </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>157.94</v>
+      </c>
+      <c r="D230" t="n">
+        <v>435802.26</v>
+      </c>
+      <c r="E230" t="n">
+        <v>314.69</v>
+      </c>
+      <c r="F230" t="n">
+        <v>138.5</v>
+      </c>
+      <c r="G230" t="n">
+        <v>138.34</v>
+      </c>
+      <c r="I230" t="n">
+        <v>164.99</v>
+      </c>
+      <c r="J230" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K230" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="L230" t="n">
+        <v>152.18</v>
+      </c>
+      <c r="M230" t="n">
+        <v>144.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M230"/>
+  <dimension ref="A1:M231"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8658,6 +8658,37 @@
         <v>144.99</v>
       </c>
     </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>455543.32</v>
+      </c>
+      <c r="E231" t="n">
+        <v>315.62</v>
+      </c>
+      <c r="F231" t="n">
+        <v>127.82</v>
+      </c>
+      <c r="G231" t="n">
+        <v>138.34</v>
+      </c>
+      <c r="J231" t="n">
+        <v>1539</v>
+      </c>
+      <c r="K231" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="L231" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="M231" t="n">
+        <v>144.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M231"/>
+  <dimension ref="A1:M232"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8689,6 +8689,37 @@
         <v>144.99</v>
       </c>
     </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>455543.32</v>
+      </c>
+      <c r="E232" t="n">
+        <v>315.62</v>
+      </c>
+      <c r="F232" t="n">
+        <v>130.33</v>
+      </c>
+      <c r="G232" t="n">
+        <v>139.09</v>
+      </c>
+      <c r="J232" t="n">
+        <v>1539</v>
+      </c>
+      <c r="K232" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="L232" t="n">
+        <v>129.63</v>
+      </c>
+      <c r="M232" t="n">
+        <v>144.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M232"/>
+  <dimension ref="A1:M233"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8720,6 +8720,37 @@
         <v>144.99</v>
       </c>
     </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>1196260.96</v>
+      </c>
+      <c r="E233" t="n">
+        <v>280.38</v>
+      </c>
+      <c r="F233" t="n">
+        <v>134.52</v>
+      </c>
+      <c r="G233" t="n">
+        <v>139.09</v>
+      </c>
+      <c r="J233" t="n">
+        <v>1559</v>
+      </c>
+      <c r="K233" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="L233" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="M233" t="n">
+        <v>144.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M233"/>
+  <dimension ref="A1:M234"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8751,6 +8751,37 @@
         <v>144.99</v>
       </c>
     </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>1196260.96</v>
+      </c>
+      <c r="E234" t="n">
+        <v>285.85</v>
+      </c>
+      <c r="F234" t="n">
+        <v>138.82</v>
+      </c>
+      <c r="G234" t="n">
+        <v>139.09</v>
+      </c>
+      <c r="J234" t="n">
+        <v>1559</v>
+      </c>
+      <c r="K234" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="L234" t="n">
+        <v>133.28</v>
+      </c>
+      <c r="M234" t="n">
+        <v>144.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M234"/>
+  <dimension ref="A1:M235"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8782,6 +8782,37 @@
         <v>144.99</v>
       </c>
     </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>1196260.96</v>
+      </c>
+      <c r="E235" t="n">
+        <v>297.55</v>
+      </c>
+      <c r="F235" t="n">
+        <v>138.63</v>
+      </c>
+      <c r="G235" t="n">
+        <v>139.09</v>
+      </c>
+      <c r="J235" t="n">
+        <v>1559</v>
+      </c>
+      <c r="K235" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="L235" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="M235" t="n">
+        <v>144.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M235"/>
+  <dimension ref="A1:M236"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8813,6 +8813,43 @@
         <v>144.99</v>
       </c>
     </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>158.3</v>
+      </c>
+      <c r="D236" t="n">
+        <v>1196260.96</v>
+      </c>
+      <c r="E236" t="n">
+        <v>297.55</v>
+      </c>
+      <c r="F236" t="n">
+        <v>128.34</v>
+      </c>
+      <c r="G236" t="n">
+        <v>139.09</v>
+      </c>
+      <c r="I236" t="n">
+        <v>159.97</v>
+      </c>
+      <c r="J236" t="n">
+        <v>1559</v>
+      </c>
+      <c r="K236" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="L236" t="n">
+        <v>118</v>
+      </c>
+      <c r="M236" t="n">
+        <v>144.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M236"/>
+  <dimension ref="A1:M237"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8850,6 +8850,43 @@
         <v>144.99</v>
       </c>
     </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>156.85</v>
+      </c>
+      <c r="D237" t="n">
+        <v>1250596.05</v>
+      </c>
+      <c r="E237" t="n">
+        <v>297.55</v>
+      </c>
+      <c r="F237" t="n">
+        <v>121.28</v>
+      </c>
+      <c r="G237" t="n">
+        <v>147.39</v>
+      </c>
+      <c r="I237" t="n">
+        <v>154.99</v>
+      </c>
+      <c r="J237" t="n">
+        <v>1564</v>
+      </c>
+      <c r="K237" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="L237" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="M237" t="n">
+        <v>154.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M237"/>
+  <dimension ref="A1:M238"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8887,6 +8887,43 @@
         <v>154.99</v>
       </c>
     </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>157.85</v>
+      </c>
+      <c r="D238" t="n">
+        <v>1250596.05</v>
+      </c>
+      <c r="E238" t="n">
+        <v>297.55</v>
+      </c>
+      <c r="F238" t="n">
+        <v>128.16</v>
+      </c>
+      <c r="G238" t="n">
+        <v>147.39</v>
+      </c>
+      <c r="I238" t="n">
+        <v>159.99</v>
+      </c>
+      <c r="J238" t="n">
+        <v>1564</v>
+      </c>
+      <c r="K238" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="L238" t="n">
+        <v>116.56</v>
+      </c>
+      <c r="M238" t="n">
+        <v>154.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M238"/>
+  <dimension ref="A1:M239"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8924,6 +8924,37 @@
         <v>154.99</v>
       </c>
     </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>1250596.05</v>
+      </c>
+      <c r="E239" t="n">
+        <v>317.35</v>
+      </c>
+      <c r="F239" t="n">
+        <v>127.66</v>
+      </c>
+      <c r="G239" t="n">
+        <v>159.16</v>
+      </c>
+      <c r="J239" t="n">
+        <v>1564</v>
+      </c>
+      <c r="K239" t="n">
+        <v>130.61</v>
+      </c>
+      <c r="L239" t="n">
+        <v>119.44</v>
+      </c>
+      <c r="M239" t="n">
+        <v>165.16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M239"/>
+  <dimension ref="A1:M240"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8955,6 +8955,37 @@
         <v>165.16</v>
       </c>
     </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>1250631.09</v>
+      </c>
+      <c r="E240" t="n">
+        <v>299.52</v>
+      </c>
+      <c r="F240" t="n">
+        <v>144.14</v>
+      </c>
+      <c r="G240" t="n">
+        <v>153.16</v>
+      </c>
+      <c r="J240" t="n">
+        <v>1539</v>
+      </c>
+      <c r="K240" t="n">
+        <v>130.61</v>
+      </c>
+      <c r="L240" t="n">
+        <v>141.66</v>
+      </c>
+      <c r="M240" t="n">
+        <v>159.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M240"/>
+  <dimension ref="A1:M241"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8986,6 +8986,37 @@
         <v>159.99</v>
       </c>
     </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>477230.24</v>
+      </c>
+      <c r="E241" t="n">
+        <v>294.91</v>
+      </c>
+      <c r="F241" t="n">
+        <v>140.68</v>
+      </c>
+      <c r="G241" t="n">
+        <v>159.16</v>
+      </c>
+      <c r="J241" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K241" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="L241" t="n">
+        <v>144.26</v>
+      </c>
+      <c r="M241" t="n">
+        <v>165.16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M241"/>
+  <dimension ref="A1:M242"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9017,6 +9017,37 @@
         <v>165.16</v>
       </c>
     </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>477230.24</v>
+      </c>
+      <c r="E242" t="n">
+        <v>294.91</v>
+      </c>
+      <c r="F242" t="n">
+        <v>148.76</v>
+      </c>
+      <c r="G242" t="n">
+        <v>159.16</v>
+      </c>
+      <c r="J242" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K242" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="L242" t="n">
+        <v>139.67</v>
+      </c>
+      <c r="M242" t="n">
+        <v>165.16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M242"/>
+  <dimension ref="A1:M243"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9048,6 +9048,37 @@
         <v>165.16</v>
       </c>
     </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>477230.24</v>
+      </c>
+      <c r="E243" t="n">
+        <v>294.91</v>
+      </c>
+      <c r="F243" t="n">
+        <v>139.86</v>
+      </c>
+      <c r="G243" t="n">
+        <v>159.16</v>
+      </c>
+      <c r="J243" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K243" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="L243" t="n">
+        <v>136.33</v>
+      </c>
+      <c r="M243" t="n">
+        <v>165.16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M243"/>
+  <dimension ref="A1:M244"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9079,6 +9079,43 @@
         <v>165.16</v>
       </c>
     </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>157.75</v>
+      </c>
+      <c r="D244" t="n">
+        <v>477230.24</v>
+      </c>
+      <c r="E244" t="n">
+        <v>294.91</v>
+      </c>
+      <c r="F244" t="n">
+        <v>137.99</v>
+      </c>
+      <c r="G244" t="n">
+        <v>157.14</v>
+      </c>
+      <c r="I244" t="n">
+        <v>164.99</v>
+      </c>
+      <c r="J244" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K244" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="L244" t="n">
+        <v>127.62</v>
+      </c>
+      <c r="M244" t="n">
+        <v>159.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M244"/>
+  <dimension ref="A1:M245"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9116,6 +9116,43 @@
         <v>159.99</v>
       </c>
     </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>152.82</v>
+      </c>
+      <c r="D245" t="n">
+        <v>477230.24</v>
+      </c>
+      <c r="E245" t="n">
+        <v>308.12</v>
+      </c>
+      <c r="F245" t="n">
+        <v>126.99</v>
+      </c>
+      <c r="G245" t="n">
+        <v>147.96</v>
+      </c>
+      <c r="I245" t="n">
+        <v>154.99</v>
+      </c>
+      <c r="J245" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K245" t="n">
+        <v>130.94</v>
+      </c>
+      <c r="L245" t="n">
+        <v>119.44</v>
+      </c>
+      <c r="M245" t="n">
+        <v>154.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M245"/>
+  <dimension ref="A1:M246"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9153,6 +9153,43 @@
         <v>154.99</v>
       </c>
     </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>153.12</v>
+      </c>
+      <c r="D246" t="n">
+        <v>477230.24</v>
+      </c>
+      <c r="E246" t="n">
+        <v>285.18</v>
+      </c>
+      <c r="F246" t="n">
+        <v>129.84</v>
+      </c>
+      <c r="G246" t="n">
+        <v>147.69</v>
+      </c>
+      <c r="I246" t="n">
+        <v>144.99</v>
+      </c>
+      <c r="J246" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K246" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="L246" t="n">
+        <v>124.47</v>
+      </c>
+      <c r="M246" t="n">
+        <v>154.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M246"/>
+  <dimension ref="A1:M247"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9190,6 +9190,43 @@
         <v>154.99</v>
       </c>
     </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>150.89</v>
+      </c>
+      <c r="D247" t="n">
+        <v>477230.24</v>
+      </c>
+      <c r="E247" t="n">
+        <v>285.18</v>
+      </c>
+      <c r="F247" t="n">
+        <v>144.63</v>
+      </c>
+      <c r="G247" t="n">
+        <v>147.69</v>
+      </c>
+      <c r="I247" t="n">
+        <v>134.99</v>
+      </c>
+      <c r="J247" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K247" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="L247" t="n">
+        <v>131.27</v>
+      </c>
+      <c r="M247" t="n">
+        <v>154.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M247"/>
+  <dimension ref="A1:M248"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9227,6 +9227,43 @@
         <v>154.99</v>
       </c>
     </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>160.03</v>
+      </c>
+      <c r="D248" t="n">
+        <v>477230.24</v>
+      </c>
+      <c r="E248" t="n">
+        <v>292.25</v>
+      </c>
+      <c r="F248" t="n">
+        <v>121.49</v>
+      </c>
+      <c r="G248" t="n">
+        <v>147.69</v>
+      </c>
+      <c r="I248" t="n">
+        <v>149.99</v>
+      </c>
+      <c r="J248" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K248" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="L248" t="n">
+        <v>123.66</v>
+      </c>
+      <c r="M248" t="n">
+        <v>154.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M248"/>
+  <dimension ref="A1:M249"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9264,6 +9264,43 @@
         <v>154.99</v>
       </c>
     </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>155.17</v>
+      </c>
+      <c r="D249" t="n">
+        <v>477230.24</v>
+      </c>
+      <c r="E249" t="n">
+        <v>300.73</v>
+      </c>
+      <c r="F249" t="n">
+        <v>141.18</v>
+      </c>
+      <c r="G249" t="n">
+        <v>147.69</v>
+      </c>
+      <c r="I249" t="n">
+        <v>144.99</v>
+      </c>
+      <c r="J249" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K249" t="n">
+        <v>130.3</v>
+      </c>
+      <c r="L249" t="n">
+        <v>137.67</v>
+      </c>
+      <c r="M249" t="n">
+        <v>154.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M249"/>
+  <dimension ref="A1:M250"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9301,6 +9301,43 @@
         <v>154.99</v>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>151.62</v>
+      </c>
+      <c r="D250" t="n">
+        <v>477230.24</v>
+      </c>
+      <c r="E250" t="n">
+        <v>300.73</v>
+      </c>
+      <c r="F250" t="n">
+        <v>129.2</v>
+      </c>
+      <c r="G250" t="n">
+        <v>157.19</v>
+      </c>
+      <c r="I250" t="n">
+        <v>134.99</v>
+      </c>
+      <c r="J250" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K250" t="n">
+        <v>130.3</v>
+      </c>
+      <c r="L250" t="n">
+        <v>126.59</v>
+      </c>
+      <c r="M250" t="n">
+        <v>159.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M250"/>
+  <dimension ref="A1:M251"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9338,6 +9338,43 @@
         <v>159.99</v>
       </c>
     </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>164.22</v>
+      </c>
+      <c r="D251" t="n">
+        <v>477230.24</v>
+      </c>
+      <c r="E251" t="n">
+        <v>299.68</v>
+      </c>
+      <c r="F251" t="n">
+        <v>129.49</v>
+      </c>
+      <c r="G251" t="n">
+        <v>158.73</v>
+      </c>
+      <c r="I251" t="n">
+        <v>164.99</v>
+      </c>
+      <c r="J251" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K251" t="n">
+        <v>130.94</v>
+      </c>
+      <c r="L251" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="M251" t="n">
+        <v>159.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M251"/>
+  <dimension ref="A1:M252"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9375,6 +9375,43 @@
         <v>159.99</v>
       </c>
     </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>166.54</v>
+      </c>
+      <c r="D252" t="n">
+        <v>1485.8</v>
+      </c>
+      <c r="E252" t="n">
+        <v>312.5</v>
+      </c>
+      <c r="F252" t="n">
+        <v>137.29</v>
+      </c>
+      <c r="G252" t="n">
+        <v>157.19</v>
+      </c>
+      <c r="I252" t="n">
+        <v>159.99</v>
+      </c>
+      <c r="J252" t="n">
+        <v>1494.5</v>
+      </c>
+      <c r="K252" t="n">
+        <v>130.94</v>
+      </c>
+      <c r="L252" t="n">
+        <v>134.62</v>
+      </c>
+      <c r="M252" t="n">
+        <v>159.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M252"/>
+  <dimension ref="A1:M253"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9412,6 +9412,43 @@
         <v>159.99</v>
       </c>
     </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>156.76</v>
+      </c>
+      <c r="D253" t="n">
+        <v>1513.8</v>
+      </c>
+      <c r="E253" t="n">
+        <v>306.86</v>
+      </c>
+      <c r="F253" t="n">
+        <v>131.85</v>
+      </c>
+      <c r="G253" t="n">
+        <v>154.19</v>
+      </c>
+      <c r="I253" t="n">
+        <v>154.99</v>
+      </c>
+      <c r="J253" t="n">
+        <v>1509</v>
+      </c>
+      <c r="K253" t="n">
+        <v>130.94</v>
+      </c>
+      <c r="L253" t="n">
+        <v>130.55</v>
+      </c>
+      <c r="M253" t="n">
+        <v>154.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M253"/>
+  <dimension ref="A1:M254"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9449,6 +9449,43 @@
         <v>154.99</v>
       </c>
     </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>147.18</v>
+      </c>
+      <c r="D254" t="n">
+        <v>1561.95</v>
+      </c>
+      <c r="E254" t="n">
+        <v>351.87</v>
+      </c>
+      <c r="F254" t="n">
+        <v>131.58</v>
+      </c>
+      <c r="G254" t="n">
+        <v>154.19</v>
+      </c>
+      <c r="I254" t="n">
+        <v>134.99</v>
+      </c>
+      <c r="J254" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K254" t="n">
+        <v>130.78</v>
+      </c>
+      <c r="L254" t="n">
+        <v>130.31</v>
+      </c>
+      <c r="M254" t="n">
+        <v>154.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M254"/>
+  <dimension ref="A1:M255"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9486,6 +9486,43 @@
         <v>154.99</v>
       </c>
     </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>147.35</v>
+      </c>
+      <c r="D255" t="n">
+        <v>1561.95</v>
+      </c>
+      <c r="E255" t="n">
+        <v>355.9</v>
+      </c>
+      <c r="F255" t="n">
+        <v>142.24</v>
+      </c>
+      <c r="G255" t="n">
+        <v>154.44</v>
+      </c>
+      <c r="I255" t="n">
+        <v>134.99</v>
+      </c>
+      <c r="J255" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K255" t="n">
+        <v>149.99</v>
+      </c>
+      <c r="L255" t="n">
+        <v>142.99</v>
+      </c>
+      <c r="M255" t="n">
+        <v>154.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M255"/>
+  <dimension ref="A1:M256"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9523,6 +9523,43 @@
         <v>154.99</v>
       </c>
     </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>146.93</v>
+      </c>
+      <c r="D256" t="n">
+        <v>1561.95</v>
+      </c>
+      <c r="E256" t="n">
+        <v>329.32</v>
+      </c>
+      <c r="F256" t="n">
+        <v>160.53</v>
+      </c>
+      <c r="G256" t="n">
+        <v>154.44</v>
+      </c>
+      <c r="I256" t="n">
+        <v>134.99</v>
+      </c>
+      <c r="J256" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K256" t="n">
+        <v>142.99</v>
+      </c>
+      <c r="L256" t="n">
+        <v>175.19</v>
+      </c>
+      <c r="M256" t="n">
+        <v>154.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M256"/>
+  <dimension ref="A1:M257"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9560,6 +9560,43 @@
         <v>154.99</v>
       </c>
     </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>153.08</v>
+      </c>
+      <c r="D257" t="n">
+        <v>1561.95</v>
+      </c>
+      <c r="E257" t="n">
+        <v>329.32</v>
+      </c>
+      <c r="F257" t="n">
+        <v>135.77</v>
+      </c>
+      <c r="G257" t="n">
+        <v>154.44</v>
+      </c>
+      <c r="I257" t="n">
+        <v>148.48</v>
+      </c>
+      <c r="J257" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K257" t="n">
+        <v>142.99</v>
+      </c>
+      <c r="L257" t="n">
+        <v>136.31</v>
+      </c>
+      <c r="M257" t="n">
+        <v>154.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M257"/>
+  <dimension ref="A1:M258"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9597,6 +9597,37 @@
         <v>154.99</v>
       </c>
     </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>152.51</v>
+      </c>
+      <c r="D258" t="n">
+        <v>1561.95</v>
+      </c>
+      <c r="F258" t="n">
+        <v>120.83</v>
+      </c>
+      <c r="G258" t="n">
+        <v>142.19</v>
+      </c>
+      <c r="I258" t="n">
+        <v>144.99</v>
+      </c>
+      <c r="J258" t="n">
+        <v>1519</v>
+      </c>
+      <c r="L258" t="n">
+        <v>107.44</v>
+      </c>
+      <c r="M258" t="n">
+        <v>149.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M258"/>
+  <dimension ref="A1:M259"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9628,6 +9628,43 @@
         <v>149.99</v>
       </c>
     </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>157.09</v>
+      </c>
+      <c r="D259" t="n">
+        <v>1561.95</v>
+      </c>
+      <c r="E259" t="n">
+        <v>329.32</v>
+      </c>
+      <c r="F259" t="n">
+        <v>134.86</v>
+      </c>
+      <c r="G259" t="n">
+        <v>142.19</v>
+      </c>
+      <c r="I259" t="n">
+        <v>149.99</v>
+      </c>
+      <c r="J259" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K259" t="n">
+        <v>142.99</v>
+      </c>
+      <c r="L259" t="n">
+        <v>119.44</v>
+      </c>
+      <c r="M259" t="n">
+        <v>149.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M259"/>
+  <dimension ref="A1:M260"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9665,6 +9665,37 @@
         <v>149.99</v>
       </c>
     </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>166.98</v>
+      </c>
+      <c r="D260" t="n">
+        <v>1561.95</v>
+      </c>
+      <c r="F260" t="n">
+        <v>129.77</v>
+      </c>
+      <c r="G260" t="n">
+        <v>153.69</v>
+      </c>
+      <c r="I260" t="n">
+        <v>164.99</v>
+      </c>
+      <c r="J260" t="n">
+        <v>1519</v>
+      </c>
+      <c r="L260" t="n">
+        <v>105.17</v>
+      </c>
+      <c r="M260" t="n">
+        <v>159.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M260"/>
+  <dimension ref="A1:M261"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9696,6 +9696,43 @@
         <v>159.99</v>
       </c>
     </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>154.63</v>
+      </c>
+      <c r="D261" t="n">
+        <v>1561.95</v>
+      </c>
+      <c r="E261" t="n">
+        <v>335.4</v>
+      </c>
+      <c r="F261" t="n">
+        <v>122.32</v>
+      </c>
+      <c r="G261" t="n">
+        <v>153.69</v>
+      </c>
+      <c r="I261" t="n">
+        <v>149.99</v>
+      </c>
+      <c r="J261" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K261" t="n">
+        <v>144.99</v>
+      </c>
+      <c r="L261" t="n">
+        <v>108.74</v>
+      </c>
+      <c r="M261" t="n">
+        <v>159.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M261"/>
+  <dimension ref="A1:M262"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9733,6 +9733,37 @@
         <v>159.99</v>
       </c>
     </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>1561.95</v>
+      </c>
+      <c r="E262" t="n">
+        <v>331.45</v>
+      </c>
+      <c r="F262" t="n">
+        <v>138.91</v>
+      </c>
+      <c r="G262" t="n">
+        <v>160.44</v>
+      </c>
+      <c r="J262" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K262" t="n">
+        <v>142.99</v>
+      </c>
+      <c r="L262" t="n">
+        <v>134.87</v>
+      </c>
+      <c r="M262" t="n">
+        <v>159.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M262"/>
+  <dimension ref="A1:M263"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9764,6 +9764,37 @@
         <v>159.99</v>
       </c>
     </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>1561.95</v>
+      </c>
+      <c r="E263" t="n">
+        <v>331.45</v>
+      </c>
+      <c r="F263" t="n">
+        <v>125.72</v>
+      </c>
+      <c r="G263" t="n">
+        <v>160.44</v>
+      </c>
+      <c r="J263" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K263" t="n">
+        <v>142.99</v>
+      </c>
+      <c r="L263" t="n">
+        <v>118.19</v>
+      </c>
+      <c r="M263" t="n">
+        <v>159.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/combined_prices.xlsx
+++ b/data/combined_prices.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M263"/>
+  <dimension ref="A1:M264"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9795,6 +9795,37 @@
         <v>159.99</v>
       </c>
     </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>1561.95</v>
+      </c>
+      <c r="E264" t="n">
+        <v>331.45</v>
+      </c>
+      <c r="F264" t="n">
+        <v>122.23</v>
+      </c>
+      <c r="G264" t="n">
+        <v>160.44</v>
+      </c>
+      <c r="J264" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K264" t="n">
+        <v>142.99</v>
+      </c>
+      <c r="L264" t="n">
+        <v>101.21</v>
+      </c>
+      <c r="M264" t="n">
+        <v>159.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
